--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_ECOCULTURE CB ALMERÍA.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_ECOCULTURE CB ALMERÍA.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>V. STRUKOV STRUKOV</t>
+          <t>A. CONTRERAS RUBIÑO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -562,76 +562,76 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D2" t="n">
-        <v>16.8945</v>
+        <v>11.7749</v>
       </c>
       <c r="E2" t="n">
-        <v>22.7567</v>
+        <v>11.7749</v>
       </c>
       <c r="F2" t="n">
-        <v>-5.8621</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.357199999999999</v>
+        <v>11.7749</v>
       </c>
       <c r="H2" t="n">
-        <v>3.911899999999998</v>
+        <v>5.1454</v>
       </c>
       <c r="I2" t="n">
-        <v>-5.269200000000001</v>
+        <v>6.6296</v>
       </c>
       <c r="J2" t="n">
-        <v>22.8825</v>
+        <v>11.7749</v>
       </c>
       <c r="K2" t="n">
-        <v>14.1884</v>
+        <v>5.1454</v>
       </c>
       <c r="L2" t="n">
-        <v>8.6938</v>
+        <v>6.6296</v>
       </c>
       <c r="M2" t="n">
-        <v>-24.2397</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>-10.2766</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>-13.9633</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>1.9824</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>-23.9847</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>25.9672</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>18.5531</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>15.3841</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>3.1688</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>-2.2835</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>8.475</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>-10.7584</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. CONTRERAS RUBIÑO</t>
+          <t>N. PEÑA BAÑOS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -640,34 +640,34 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>11.7749</v>
+        <v>9.966899999999999</v>
       </c>
       <c r="E3" t="n">
-        <v>11.7749</v>
+        <v>9.966899999999999</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>11.7749</v>
+        <v>9.966899999999999</v>
       </c>
       <c r="H3" t="n">
-        <v>5.1454</v>
+        <v>5.1453</v>
       </c>
       <c r="I3" t="n">
-        <v>6.6296</v>
+        <v>4.8213</v>
       </c>
       <c r="J3" t="n">
-        <v>11.7749</v>
+        <v>9.966899999999999</v>
       </c>
       <c r="K3" t="n">
-        <v>5.1454</v>
+        <v>5.1453</v>
       </c>
       <c r="L3" t="n">
-        <v>6.6296</v>
+        <v>4.8213</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>N. PEÑA BAÑOS</t>
+          <t>V. STRUKOV STRUKOV</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,70 +718,70 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="D4" t="n">
-        <v>9.966899999999999</v>
+        <v>2.2799</v>
       </c>
       <c r="E4" t="n">
-        <v>9.966899999999999</v>
+        <v>9.99</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>-7.7101</v>
       </c>
       <c r="G4" t="n">
-        <v>9.966899999999999</v>
+        <v>-1.357199999999999</v>
       </c>
       <c r="H4" t="n">
-        <v>5.1453</v>
+        <v>3.911899999999998</v>
       </c>
       <c r="I4" t="n">
-        <v>4.8213</v>
+        <v>-5.269200000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>9.966899999999999</v>
+        <v>22.8825</v>
       </c>
       <c r="K4" t="n">
-        <v>5.1453</v>
+        <v>14.1884</v>
       </c>
       <c r="L4" t="n">
-        <v>4.8213</v>
+        <v>8.6938</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>-24.2397</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>-10.2766</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>-13.9633</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1.9824</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-23.9847</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>25.9672</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>3.9384</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.6174</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.321</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>-2.2835</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>8.475</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-10.7584</v>
       </c>
     </row>
     <row r="5">
@@ -877,10 +877,10 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.0624</v>
+        <v>0.0395</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.0624</v>
+        <v>0.0395</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -922,10 +922,10 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.0624</v>
+        <v>0.0395</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0624</v>
+        <v>0.0395</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.4161</v>
+        <v>-0.2581</v>
       </c>
       <c r="E7" t="n">
-        <v>0.4944</v>
+        <v>0.5962</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.9105</v>
+        <v>-0.8542999999999999</v>
       </c>
       <c r="G7" t="n">
         <v>0.08550000000000001</v>
@@ -1000,13 +1000,13 @@
         <v>0.7929</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.08740000000000001</v>
+        <v>0.0707</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1248</v>
+        <v>-0.0229</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0374</v>
+        <v>0.0936</v>
       </c>
       <c r="V7" t="n">
         <v>-1.2071</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.7779</v>
+        <v>-0.7322</v>
       </c>
       <c r="E8" t="n">
-        <v>0.4475</v>
+        <v>0.5493</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.2254</v>
+        <v>-1.2816</v>
       </c>
       <c r="G8" t="n">
         <v>-1.8725</v>
@@ -1078,13 +1078,13 @@
         <v>0.9911</v>
       </c>
       <c r="S8" t="n">
-        <v>0.37</v>
+        <v>0.4158</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0072</v>
+        <v>0.0946</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3773</v>
+        <v>0.3211</v>
       </c>
       <c r="V8" t="n">
         <v>-0.2666</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.6285</v>
+        <v>-1.2563</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.9969</v>
+        <v>-0.7931</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.6317</v>
+        <v>-0.4632</v>
       </c>
       <c r="G9" t="n">
         <v>-1.8987</v>
@@ -1156,13 +1156,13 @@
         <v>0.7929</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5227000000000001</v>
+        <v>-0.1505</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4992</v>
+        <v>-0.2954</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0235</v>
+        <v>0.145</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>-6.5141</v>
+        <v>-5.043</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.6923</v>
+        <v>-2.3057</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.8216</v>
+        <v>-2.7373</v>
       </c>
       <c r="G10" t="n">
         <v>-4.1245</v>
@@ -1234,13 +1234,13 @@
         <v>2.1805</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.7683</v>
+        <v>-0.2973000000000001</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.3617</v>
+        <v>0.02500000000000002</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4065</v>
+        <v>-0.3223</v>
       </c>
       <c r="V10" t="n">
         <v>-1.8107</v>
@@ -1267,13 +1267,13 @@
         <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>-7.8607</v>
+        <v>-6.4322</v>
       </c>
       <c r="E11" t="n">
-        <v>-8.8908</v>
+        <v>-7.9115</v>
       </c>
       <c r="F11" t="n">
-        <v>1.0301</v>
+        <v>1.4793</v>
       </c>
       <c r="G11" t="n">
         <v>-4.7046</v>
@@ -1312,13 +1312,13 @@
         <v>1.9822</v>
       </c>
       <c r="S11" t="n">
-        <v>-2.2333</v>
+        <v>-0.8048</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.3728</v>
+        <v>-0.3935</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.8605</v>
+        <v>-0.4113</v>
       </c>
       <c r="V11" t="n">
         <v>0.2666</v>
@@ -1345,13 +1345,13 @@
         <v>10</v>
       </c>
       <c r="D12" t="n">
-        <v>-10.0878</v>
+        <v>-12.1276</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.0819</v>
+        <v>-6.7284</v>
       </c>
       <c r="F12" t="n">
-        <v>-5.0061</v>
+        <v>-5.3991</v>
       </c>
       <c r="G12" t="n">
         <v>-7.5704</v>
@@ -1390,13 +1390,13 @@
         <v>7.136</v>
       </c>
       <c r="S12" t="n">
-        <v>0.6703999999999999</v>
+        <v>-1.369</v>
       </c>
       <c r="T12" t="n">
-        <v>0.6578999999999999</v>
+        <v>-0.9889</v>
       </c>
       <c r="U12" t="n">
-        <v>0.01289999999999999</v>
+        <v>-0.3804999999999999</v>
       </c>
       <c r="V12" t="n">
         <v>-6.1612</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>E. LALI VICENTE UCHUATE</t>
+          <t>O. GARCIA JIMENEZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D13" t="n">
-        <v>-11.7517</v>
+        <v>-13.4086</v>
       </c>
       <c r="E13" t="n">
-        <v>-15.9533</v>
+        <v>-8.9238</v>
       </c>
       <c r="F13" t="n">
-        <v>4.2017</v>
+        <v>-4.4847</v>
       </c>
       <c r="G13" t="n">
-        <v>-15.8246</v>
+        <v>-13.2787</v>
       </c>
       <c r="H13" t="n">
-        <v>-6.3596</v>
+        <v>-9.4764</v>
       </c>
       <c r="I13" t="n">
-        <v>-9.465</v>
+        <v>-3.8023</v>
       </c>
       <c r="J13" t="n">
-        <v>-6.058400000000001</v>
+        <v>1.3673</v>
       </c>
       <c r="K13" t="n">
-        <v>2.9442</v>
+        <v>2.2564</v>
       </c>
       <c r="L13" t="n">
-        <v>-9.0023</v>
+        <v>-0.8889999999999999</v>
       </c>
       <c r="M13" t="n">
-        <v>-9.7666</v>
+        <v>-14.6461</v>
       </c>
       <c r="N13" t="n">
-        <v>-9.303800000000001</v>
+        <v>-11.7329</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.4623999999999999</v>
+        <v>-2.9131</v>
       </c>
       <c r="P13" t="n">
-        <v>6.7395</v>
+        <v>3.3698</v>
       </c>
       <c r="Q13" t="n">
-        <v>-14.0737</v>
+        <v>-10.1093</v>
       </c>
       <c r="R13" t="n">
-        <v>20.8133</v>
+        <v>13.4791</v>
       </c>
       <c r="S13" t="n">
-        <v>3.4355</v>
+        <v>-5.6471</v>
       </c>
       <c r="T13" t="n">
-        <v>2.9163</v>
+        <v>-2.9181</v>
       </c>
       <c r="U13" t="n">
-        <v>0.5188000000000001</v>
+        <v>-2.7292</v>
       </c>
       <c r="V13" t="n">
-        <v>-6.1019</v>
+        <v>2.1477</v>
       </c>
       <c r="W13" t="n">
-        <v>1.2624</v>
+        <v>2.7361</v>
       </c>
       <c r="X13" t="n">
-        <v>-7.3645</v>
+        <v>-0.5883999999999998</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>N. PENA BANOS</t>
+          <t>E. LALI VICENTE UCHUATE</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,76 +1498,76 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D14" t="n">
-        <v>-13.3191</v>
+        <v>-13.5171</v>
       </c>
       <c r="E14" t="n">
-        <v>-14.967</v>
+        <v>-17.9155</v>
       </c>
       <c r="F14" t="n">
-        <v>1.6478</v>
+        <v>4.3984</v>
       </c>
       <c r="G14" t="n">
-        <v>-45.0274</v>
+        <v>-15.8246</v>
       </c>
       <c r="H14" t="n">
-        <v>-32.0039</v>
+        <v>-6.3596</v>
       </c>
       <c r="I14" t="n">
-        <v>-13.0238</v>
+        <v>-9.465</v>
       </c>
       <c r="J14" t="n">
-        <v>-16.76</v>
+        <v>-6.058400000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>-15.3055</v>
+        <v>2.9442</v>
       </c>
       <c r="L14" t="n">
-        <v>-1.4542</v>
+        <v>-9.0023</v>
       </c>
       <c r="M14" t="n">
-        <v>-28.2679</v>
+        <v>-9.7666</v>
       </c>
       <c r="N14" t="n">
-        <v>-16.6982</v>
+        <v>-9.303800000000001</v>
       </c>
       <c r="O14" t="n">
-        <v>-11.5698</v>
+        <v>-0.4623999999999999</v>
       </c>
       <c r="P14" t="n">
-        <v>-6.7395</v>
+        <v>6.7395</v>
       </c>
       <c r="Q14" t="n">
-        <v>-33.8958</v>
+        <v>-14.0737</v>
       </c>
       <c r="R14" t="n">
-        <v>27.1567</v>
+        <v>20.8133</v>
       </c>
       <c r="S14" t="n">
-        <v>31.538</v>
+        <v>1.6696</v>
       </c>
       <c r="T14" t="n">
-        <v>18.4422</v>
+        <v>0.9542</v>
       </c>
       <c r="U14" t="n">
-        <v>13.0958</v>
+        <v>0.7153999999999998</v>
       </c>
       <c r="V14" t="n">
-        <v>6.909500000000001</v>
+        <v>-6.1019</v>
       </c>
       <c r="W14" t="n">
-        <v>17.2467</v>
+        <v>1.2624</v>
       </c>
       <c r="X14" t="n">
-        <v>-10.337</v>
+        <v>-7.3645</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>O. GARCIA JIMENEZ</t>
+          <t>F. GARCIA GARRIDO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,76 +1576,76 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D15" t="n">
-        <v>-16.1573</v>
+        <v>-20.204</v>
       </c>
       <c r="E15" t="n">
-        <v>-10.4978</v>
+        <v>-1.9493</v>
       </c>
       <c r="F15" t="n">
-        <v>-5.6594</v>
+        <v>-18.2544</v>
       </c>
       <c r="G15" t="n">
-        <v>-13.2787</v>
+        <v>-6.4278</v>
       </c>
       <c r="H15" t="n">
-        <v>-9.4764</v>
+        <v>-5.4592</v>
       </c>
       <c r="I15" t="n">
-        <v>-3.8023</v>
+        <v>-0.9684999999999997</v>
       </c>
       <c r="J15" t="n">
-        <v>1.3673</v>
+        <v>9.439599999999999</v>
       </c>
       <c r="K15" t="n">
-        <v>2.2564</v>
+        <v>4.5352</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.8889999999999999</v>
+        <v>4.9044</v>
       </c>
       <c r="M15" t="n">
-        <v>-14.6461</v>
+        <v>-15.8674</v>
       </c>
       <c r="N15" t="n">
-        <v>-11.7329</v>
+        <v>-9.9948</v>
       </c>
       <c r="O15" t="n">
-        <v>-2.9131</v>
+        <v>-5.8729</v>
       </c>
       <c r="P15" t="n">
-        <v>3.3698</v>
+        <v>0.1982</v>
       </c>
       <c r="Q15" t="n">
-        <v>-10.1093</v>
+        <v>-12.8843</v>
       </c>
       <c r="R15" t="n">
-        <v>13.4791</v>
+        <v>13.0826</v>
       </c>
       <c r="S15" t="n">
-        <v>-8.396100000000001</v>
+        <v>-3.8699</v>
       </c>
       <c r="T15" t="n">
-        <v>-4.492</v>
+        <v>-2.0555</v>
       </c>
       <c r="U15" t="n">
-        <v>-3.9041</v>
+        <v>-1.8141</v>
       </c>
       <c r="V15" t="n">
-        <v>2.1477</v>
+        <v>-10.1046</v>
       </c>
       <c r="W15" t="n">
-        <v>2.7361</v>
+        <v>3.5509</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.5883999999999998</v>
+        <v>-13.6555</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>F. GARCIA GARRIDO</t>
+          <t>P. BILEISIS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1654,70 +1654,70 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D16" t="n">
-        <v>-23.6462</v>
+        <v>-23.6967</v>
       </c>
       <c r="E16" t="n">
-        <v>-4.558800000000001</v>
+        <v>-12.917</v>
       </c>
       <c r="F16" t="n">
-        <v>-19.0877</v>
+        <v>-10.7798</v>
       </c>
       <c r="G16" t="n">
-        <v>-6.4278</v>
+        <v>-32.0481</v>
       </c>
       <c r="H16" t="n">
-        <v>-5.4592</v>
+        <v>-11.8433</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.9684999999999997</v>
+        <v>-20.2046</v>
       </c>
       <c r="J16" t="n">
-        <v>9.439599999999999</v>
+        <v>9.369300000000001</v>
       </c>
       <c r="K16" t="n">
-        <v>4.5352</v>
+        <v>10.1065</v>
       </c>
       <c r="L16" t="n">
-        <v>4.9044</v>
+        <v>-0.7373999999999992</v>
       </c>
       <c r="M16" t="n">
-        <v>-15.8674</v>
+        <v>-41.417</v>
       </c>
       <c r="N16" t="n">
-        <v>-9.9948</v>
+        <v>-21.9497</v>
       </c>
       <c r="O16" t="n">
-        <v>-5.8729</v>
+        <v>-19.4673</v>
       </c>
       <c r="P16" t="n">
-        <v>0.1982</v>
+        <v>10.1096</v>
       </c>
       <c r="Q16" t="n">
-        <v>-12.8843</v>
+        <v>-38.2567</v>
       </c>
       <c r="R16" t="n">
-        <v>13.0826</v>
+        <v>48.3665</v>
       </c>
       <c r="S16" t="n">
-        <v>-7.312</v>
+        <v>-20.2661</v>
       </c>
       <c r="T16" t="n">
-        <v>-4.6649</v>
+        <v>-11.7626</v>
       </c>
       <c r="U16" t="n">
-        <v>-2.6474</v>
+        <v>-8.503500000000001</v>
       </c>
       <c r="V16" t="n">
-        <v>-10.1046</v>
+        <v>18.5079</v>
       </c>
       <c r="W16" t="n">
-        <v>3.5509</v>
+        <v>27.7332</v>
       </c>
       <c r="X16" t="n">
-        <v>-13.6555</v>
+        <v>-9.2255</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>8</v>
       </c>
       <c r="D17" t="n">
-        <v>-25.479</v>
+        <v>-23.8686</v>
       </c>
       <c r="E17" t="n">
-        <v>-18.6775</v>
+        <v>-17.4322</v>
       </c>
       <c r="F17" t="n">
-        <v>-6.801600000000001</v>
+        <v>-6.4365</v>
       </c>
       <c r="G17" t="n">
         <v>-7.7977</v>
@@ -1780,13 +1780,13 @@
         <v>5.7483</v>
       </c>
       <c r="S17" t="n">
-        <v>-4.091699999999999</v>
+        <v>-2.4813</v>
       </c>
       <c r="T17" t="n">
-        <v>-3.2299</v>
+        <v>-1.9845</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.8618999999999999</v>
+        <v>-0.4969</v>
       </c>
       <c r="V17" t="n">
         <v>-4.4713</v>
@@ -1813,13 +1813,13 @@
         <v>18</v>
       </c>
       <c r="D18" t="n">
-        <v>-27.331</v>
+        <v>-24.0285</v>
       </c>
       <c r="E18" t="n">
-        <v>-15.8994</v>
+        <v>-10.7306</v>
       </c>
       <c r="F18" t="n">
-        <v>-11.432</v>
+        <v>-13.2983</v>
       </c>
       <c r="G18" t="n">
         <v>-39.3138</v>
@@ -1858,13 +1858,13 @@
         <v>36.0765</v>
       </c>
       <c r="S18" t="n">
-        <v>-6.6299</v>
+        <v>-3.3277</v>
       </c>
       <c r="T18" t="n">
-        <v>-9.096500000000001</v>
+        <v>-3.9281</v>
       </c>
       <c r="U18" t="n">
-        <v>2.4666</v>
+        <v>0.6006000000000002</v>
       </c>
       <c r="V18" t="n">
         <v>7.7103</v>
@@ -1891,13 +1891,13 @@
         <v>21</v>
       </c>
       <c r="D19" t="n">
-        <v>-33.4356</v>
+        <v>-24.4426</v>
       </c>
       <c r="E19" t="n">
-        <v>-12.8069</v>
+        <v>-7.9375</v>
       </c>
       <c r="F19" t="n">
-        <v>-20.6285</v>
+        <v>-16.5046</v>
       </c>
       <c r="G19" t="n">
         <v>8.4809</v>
@@ -1936,13 +1936,13 @@
         <v>42.0233</v>
       </c>
       <c r="S19" t="n">
-        <v>-17.9303</v>
+        <v>-8.937099999999999</v>
       </c>
       <c r="T19" t="n">
-        <v>-10.1755</v>
+        <v>-5.3062</v>
       </c>
       <c r="U19" t="n">
-        <v>-7.7545</v>
+        <v>-3.6309</v>
       </c>
       <c r="V19" t="n">
         <v>-2.3802</v>
@@ -1969,13 +1969,13 @@
         <v>19</v>
       </c>
       <c r="D20" t="n">
-        <v>-35.2331</v>
+        <v>-33.8546</v>
       </c>
       <c r="E20" t="n">
-        <v>-25.7162</v>
+        <v>-26.6266</v>
       </c>
       <c r="F20" t="n">
-        <v>-9.516699999999998</v>
+        <v>-7.2279</v>
       </c>
       <c r="G20" t="n">
         <v>-18.4994</v>
@@ -2014,13 +2014,13 @@
         <v>18.4347</v>
       </c>
       <c r="S20" t="n">
-        <v>-3.4474</v>
+        <v>-2.0692</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1448000000000004</v>
+        <v>-0.7656000000000001</v>
       </c>
       <c r="U20" t="n">
-        <v>-3.5923</v>
+        <v>-1.3033</v>
       </c>
       <c r="V20" t="n">
         <v>-6.7447</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>P. BILEISIS</t>
+          <t>N. PENA BANOS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2044,70 +2044,70 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="D21" t="n">
-        <v>-45.2724</v>
+        <v>-35.0894</v>
       </c>
       <c r="E21" t="n">
-        <v>-26.1562</v>
+        <v>-29.9851</v>
       </c>
       <c r="F21" t="n">
-        <v>-19.1161</v>
+        <v>-5.1043</v>
       </c>
       <c r="G21" t="n">
-        <v>-32.0481</v>
+        <v>-45.0274</v>
       </c>
       <c r="H21" t="n">
-        <v>-11.8433</v>
+        <v>-32.0039</v>
       </c>
       <c r="I21" t="n">
-        <v>-20.2046</v>
+        <v>-13.0238</v>
       </c>
       <c r="J21" t="n">
-        <v>9.369300000000001</v>
+        <v>-16.76</v>
       </c>
       <c r="K21" t="n">
-        <v>10.1065</v>
+        <v>-15.3055</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.7373999999999992</v>
+        <v>-1.4542</v>
       </c>
       <c r="M21" t="n">
-        <v>-41.417</v>
+        <v>-28.2679</v>
       </c>
       <c r="N21" t="n">
-        <v>-21.9497</v>
+        <v>-16.6982</v>
       </c>
       <c r="O21" t="n">
-        <v>-19.4673</v>
+        <v>-11.5698</v>
       </c>
       <c r="P21" t="n">
-        <v>10.1096</v>
+        <v>-6.7395</v>
       </c>
       <c r="Q21" t="n">
-        <v>-38.2567</v>
+        <v>-33.8958</v>
       </c>
       <c r="R21" t="n">
-        <v>48.3665</v>
+        <v>27.1567</v>
       </c>
       <c r="S21" t="n">
-        <v>-41.8416</v>
+        <v>9.7682</v>
       </c>
       <c r="T21" t="n">
-        <v>-25.0015</v>
+        <v>3.4245</v>
       </c>
       <c r="U21" t="n">
-        <v>-16.8398</v>
+        <v>6.3438</v>
       </c>
       <c r="V21" t="n">
-        <v>18.5079</v>
+        <v>6.909500000000001</v>
       </c>
       <c r="W21" t="n">
-        <v>27.7332</v>
+        <v>17.2467</v>
       </c>
       <c r="X21" t="n">
-        <v>-9.2255</v>
+        <v>-10.337</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>25</v>
       </c>
       <c r="D22" t="n">
-        <v>-55.6156</v>
+        <v>-47.2671</v>
       </c>
       <c r="E22" t="n">
-        <v>-34.8943</v>
+        <v>-29.3642</v>
       </c>
       <c r="F22" t="n">
-        <v>-20.7212</v>
+        <v>-17.9029</v>
       </c>
       <c r="G22" t="n">
         <v>-25.0519</v>
@@ -2170,13 +2170,13 @@
         <v>36.0766</v>
       </c>
       <c r="S22" t="n">
-        <v>-18.7571</v>
+        <v>-10.4083</v>
       </c>
       <c r="T22" t="n">
-        <v>-12.2869</v>
+        <v>-6.7564</v>
       </c>
       <c r="U22" t="n">
-        <v>-6.4702</v>
+        <v>-3.6517</v>
       </c>
       <c r="V22" t="n">
         <v>-3.8777</v>
@@ -2203,13 +2203,13 @@
         <v>26</v>
       </c>
       <c r="D23" t="n">
-        <v>-62.4356</v>
+        <v>-59.6713</v>
       </c>
       <c r="E23" t="n">
-        <v>-34.5394</v>
+        <v>-36.0253</v>
       </c>
       <c r="F23" t="n">
-        <v>-27.8962</v>
+        <v>-23.6461</v>
       </c>
       <c r="G23" t="n">
         <v>-40.5143</v>
@@ -2248,13 +2248,13 @@
         <v>45.7894</v>
       </c>
       <c r="S23" t="n">
-        <v>-12.4788</v>
+        <v>-9.714399999999999</v>
       </c>
       <c r="T23" t="n">
-        <v>-4.6094</v>
+        <v>-6.0953</v>
       </c>
       <c r="U23" t="n">
-        <v>-7.8694</v>
+        <v>-3.619</v>
       </c>
       <c r="V23" t="n">
         <v>-13.2091</v>
@@ -2281,13 +2281,13 @@
         <v>25</v>
       </c>
       <c r="D24" t="n">
-        <v>-65.0891</v>
+        <v>-63.6623</v>
       </c>
       <c r="E24" t="n">
-        <v>-59.1481</v>
+        <v>-54.35760000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>-5.941199999999999</v>
+        <v>-9.3047</v>
       </c>
       <c r="G24" t="n">
         <v>-36.1617</v>
@@ -2326,13 +2326,13 @@
         <v>46.5823</v>
       </c>
       <c r="S24" t="n">
-        <v>-7.4494</v>
+        <v>-6.022600000000001</v>
       </c>
       <c r="T24" t="n">
-        <v>-14.0986</v>
+        <v>-9.308299999999999</v>
       </c>
       <c r="U24" t="n">
-        <v>6.6488</v>
+        <v>3.2853</v>
       </c>
       <c r="V24" t="n">
         <v>-3.0429</v>
@@ -2359,13 +2359,13 @@
         <v>26</v>
       </c>
       <c r="D25" t="n">
-        <v>-402.5689000000001</v>
+        <v>-383.591</v>
       </c>
       <c r="E25" t="n">
-        <v>-246.1908</v>
+        <v>-238.0786</v>
       </c>
       <c r="F25" t="n">
-        <v>-156.3784</v>
+        <v>-145.5121</v>
       </c>
       <c r="G25" t="n">
         <v>-270.2571</v>
@@ -2377,7 +2377,7 @@
         <v>-130.8909</v>
       </c>
       <c r="J25" t="n">
-        <v>86.4238</v>
+        <v>86.42380000000001</v>
       </c>
       <c r="K25" t="n">
         <v>75.6831</v>
@@ -2401,19 +2401,19 @@
         <v>-421.2209</v>
       </c>
       <c r="R25" t="n">
-        <v>393.4721</v>
+        <v>393.4721000000001</v>
       </c>
       <c r="S25" t="n">
-        <v>-78.44139999999999</v>
+        <v>-59.4631</v>
       </c>
       <c r="T25" t="n">
-        <v>-53.538</v>
+        <v>-45.42610000000001</v>
       </c>
       <c r="U25" t="n">
-        <v>-24.90369999999999</v>
+        <v>-14.0369</v>
       </c>
       <c r="V25" t="n">
-        <v>-26.11950000000001</v>
+        <v>-26.1195</v>
       </c>
       <c r="W25" t="n">
         <v>142.1475</v>
